--- a/fix-fhirpath-valueCodeableConcept/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/fix-fhirpath-valueCodeableConcept/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:42:47+00:00</t>
+    <t>2026-07-01T08:54:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -468,7 +468,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {(extension.where(url='motivation').valueCodeableConcept.coding.where(code='9999').exists()) implies (extension.where(url='motivationLocale').valueString.exists())}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').valueCodeableConcept.coding.where(code='5').exists()) implies (extension.where(url='dateEffetCloture').exists())}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {(extension.where(url='motivation').value.ofType(CodeableConcept).coding.where(code='9999').exists()) implies (extension.where(url='motivationLocale').value.ofType(String).exists())}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').value.ofType(CodeableConcept).coding.where(code='5').exists()) implies (extension.where(url='dateEffetCloture').exists())}</t>
   </si>
   <si>
     <t>Basic.extension:TDDUIDecision.id</t>
@@ -688,8 +688,8 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}FormationCardinality:Formation est obligatoire si typeDroitPrestation = '11.1' (Orientation en Centre de rééducation professionnelle (CRP)). {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='11.1') implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='formation'))}PrecisionOrientationValues7.8:Si typeDroitPrestation = '7.8' (Orientation vers un Service d'éducation spéciale et de soins à domicile (SESSAD)) alors precisionOrientation entre '1' et
- '6' {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.8') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=1) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=6))}PrecisionOrientationValues7.9:Si typeDroitPrestation = '7.9' (Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP)) alors precisionOrientation entre '7' et '8' {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='7.9') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=7) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=8))}PrecisionOrientationValues13.1-13.2:Si typeDroitPrestation = '13.1' (Orientation vers un établissement d'accueil non médicalisé) ou '13.2' (Orientation vers un établissement d'accueil médicalisé en tout ou partie) alors precisionOrientation est interdit {((extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='13.1') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='13.2')) implies (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').not())}PrecisionOrientationValues8.3:Si typeDroitPrestation = '8.3' (Orientation en Enseignement adapté (SEGPA/EREA)) alors precisionOrientation entre '9' et '10'  {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.3') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&gt;=9) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code.toInteger()&lt;=10))}PrecisionOrientationValues8.6:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) alors precisionOrientation = 'UEA' (Unité d'enseignement élémentaire autisme) ou 'UEM' (Unité d'enseignement en maternelle plan autisme). {(extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.6') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code='UEA') or (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').valueCodeableConcept.coding.code='UEM'))}temporaliteAccueilCardinalityViaCategorieDroitPrestation:Si categorieDroitPrestation = '13' (Orientation ESMS Adultes) ou '7' (Orientation ESMS Enfants) alors temporaliteAccueil est obligatoire. {((extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='13') or (extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7')) implies (extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil'))}temporaliteAccueilCardinalityViaTypeDroitPrestation:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) ou '8.7' (Orientation vers une Scolarisation en milieu ordinaire à temps partagé) ou '8.8' (Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé) ou '8.10' (Orientation vers une unité d'enseignement et une scolarisation en enseignement adapté à temps partagé) alors la temporalité d'accueil est obligatoire. {((extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.6') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.7') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.8') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code='8.10')) implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil'))}cretonCardinality:Si categorieDroitPrestation = '7' (ESSMS enfant) alors Creton est obligatoire {((extension.where(url='categorieDroitPrestation').valueCodeableConcept.coding.code='7') or (extension.where(url='typeDroitPrestation').valueCodeableConcept.coding.code.matches('^7[.][0-9]+$'))) implies (extension.where(url='creton'))}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}FormationCardinality:Formation est obligatoire si typeDroitPrestation = '11.1' (Orientation en Centre de rééducation professionnelle (CRP)). {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.code='11.1') implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='formation'))}PrecisionOrientationValues7.8:Si typeDroitPrestation = '7.8' (Orientation vers un Service d'éducation spéciale et de soins à domicile (SESSAD)) alors precisionOrientation entre '1' et
+ '6' {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.code='7.8') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.code.toInteger()&gt;=1) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.code.toInteger()&lt;=6))}PrecisionOrientationValues7.9:Si typeDroitPrestation = '7.9' (Orientation vers un Service d'accompagnement familial et d'éducation précoce (SAFEP)) alors precisionOrientation entre '7' et '8' {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.code='7.9') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.code.toInteger()&gt;=7) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.code.toInteger()&lt;=8))}PrecisionOrientationValues13.1-13.2:Si typeDroitPrestation = '13.1' (Orientation vers un établissement d'accueil non médicalisé) ou '13.2' (Orientation vers un établissement d'accueil médicalisé en tout ou partie) alors precisionOrientation est interdit {((extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.code='13.1') or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.code='13.2')) implies (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').not())}PrecisionOrientationValues8.3:Si typeDroitPrestation = '8.3' (Orientation en Enseignement adapté (SEGPA/EREA)) alors precisionOrientation entre '9' et '10'  {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.code='8.3') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.code.toInteger()&gt;=9) and (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.code.toInteger()&lt;=10))}PrecisionOrientationValues8.6:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) alors precisionOrientation = 'UEA' (Unité d'enseignement élémentaire autisme) ou 'UEM' (Unité d'enseignement en maternelle plan autisme). {(extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.code='8.6') implies ((extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.code='UEA') or (extension.where(url='detailPrestation').extension.where(url='precisionOrientation').value.ofType(CodeableConcept).coding.code='UEM'))}temporaliteAccueilCardinalityViaCategorieDroitPrestation:Si categorieDroitPrestation = '13' (Orientation ESMS Adultes) ou '7' (Orientation ESMS Enfants) alors temporaliteAccueil est obligatoire. {((extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.code='13') or (extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.code='7')) implies (extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil'))}temporaliteAccueilCardinalityViaTypeDroitPrestation:Si typeDroitPrestation = '8.6' (Orientation en Unité d'enseignement) ou '8.7' (Orientation vers une Scolarisation en milieu ordinaire à temps partagé) ou '8.8' (Orientation vers une Unité d'enseignement et une scolarisation en ULIS à temps partagé) ou '8.10' (Orientation vers une unité d'enseignement et une scolarisation en enseignement adapté à temps partagé) alors la temporalité d'accueil est obligatoire. {((extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.code='8.6') or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.code='8.7') or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.code='8.8') or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.code='8.10')) implies (extension.where(url='droitPrestation').extension.where(url='detailPrestation').extension.where(url='temporaliteAccueil'))}cretonCardinality:Si categorieDroitPrestation = '7' (ESSMS enfant) alors Creton est obligatoire {((extension.where(url='categorieDroitPrestation').value.ofType(CodeableConcept).coding.code='7') or (extension.where(url='typeDroitPrestation').value.ofType(CodeableConcept).coding.code.matches('^7[.][0-9]+$'))) implies (extension.where(url='creton'))}</t>
   </si>
   <si>
     <t>DroitPrestation</t>

--- a/fix-fhirpath-valueCodeableConcept/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/fix-fhirpath-valueCodeableConcept/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:54:05+00:00</t>
+    <t>2026-07-01T10:22:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -468,7 +468,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {(extension.where(url='motivation').value.ofType(CodeableConcept).coding.where(code='9999').exists()) implies (extension.where(url='motivationLocale').value.ofType(String).exists())}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').value.ofType(CodeableConcept).coding.where(code='5').exists()) implies (extension.where(url='dateEffetCloture').exists())}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}motivationLocaleRequired:La motivation locale doit être renseignée si la motivation de la décision est '9999' (Autre). {(extension.where(url='motivation').value.ofType(CodeableConcept).coding.where(code='9999').exists()) implies (extension.where(url='motivationLocale').value.ofType(string).exists())}DateEffetClotureCardinality:Si typeDecision = '5' (Clôture de droit) alors dateEffetCloture est obligatoire. {(extension.where(url='typeDecision').value.ofType(CodeableConcept).coding.where(code='5').exists()) implies (extension.where(url='dateEffetCloture').exists())}</t>
   </si>
   <si>
     <t>Basic.extension:TDDUIDecision.id</t>

--- a/fix-fhirpath-valueCodeableConcept/ig/StructureDefinition-tddui-basic-decision.xlsx
+++ b/fix-fhirpath-valueCodeableConcept/ig/StructureDefinition-tddui-basic-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:22:46+00:00</t>
+    <t>2026-07-01T11:17:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
